--- a/results/evaluation/error_candidates.xlsx
+++ b/results/evaluation/error_candidates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MinhChau\VSCode\python\System_Sematic_Search_Truyen\results\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC99D2A0-3BD6-4641-A0EC-58EAD023A757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BC79D2-9CF4-4259-89A2-1D50DB72FE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="error_candidates" sheetId="1" r:id="rId1"/>
@@ -3252,7 +3252,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T649"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3323,7 +3322,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -3382,7 +3381,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -3559,7 +3558,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -3618,7 +3617,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -3677,7 +3676,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -3736,7 +3735,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -3795,7 +3794,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -3854,7 +3853,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -3913,7 +3912,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -3972,7 +3971,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -4031,7 +4030,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>58</v>
       </c>
@@ -4090,7 +4089,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -4149,7 +4148,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -4208,7 +4207,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -4267,7 +4266,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>102</v>
       </c>
@@ -4326,7 +4325,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -4385,7 +4384,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -4444,7 +4443,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -4503,7 +4502,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -4562,7 +4561,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>117</v>
       </c>
@@ -4621,7 +4620,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -4680,7 +4679,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>117</v>
       </c>
@@ -4739,7 +4738,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>135</v>
       </c>
@@ -4798,7 +4797,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>135</v>
       </c>
@@ -4857,7 +4856,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>135</v>
       </c>
@@ -4916,7 +4915,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>135</v>
       </c>
@@ -4975,7 +4974,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>135</v>
       </c>
@@ -5034,7 +5033,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>135</v>
       </c>
@@ -5093,7 +5092,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>135</v>
       </c>
@@ -5152,7 +5151,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>135</v>
       </c>
@@ -5211,7 +5210,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>135</v>
       </c>
@@ -5270,7 +5269,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>152</v>
       </c>
@@ -5329,7 +5328,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -5388,7 +5387,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>152</v>
       </c>
@@ -5447,7 +5446,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>159</v>
       </c>
@@ -5506,7 +5505,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>162</v>
       </c>
@@ -5565,7 +5564,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>162</v>
       </c>
@@ -5624,7 +5623,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>162</v>
       </c>
@@ -5683,7 +5682,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>162</v>
       </c>
@@ -5742,7 +5741,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>162</v>
       </c>
@@ -5801,7 +5800,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>162</v>
       </c>
@@ -5860,7 +5859,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>162</v>
       </c>
@@ -5919,7 +5918,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>162</v>
       </c>
@@ -5978,7 +5977,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>176</v>
       </c>
@@ -6037,7 +6036,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>176</v>
       </c>
@@ -6096,7 +6095,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>176</v>
       </c>
@@ -6155,7 +6154,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>176</v>
       </c>
@@ -6214,7 +6213,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>176</v>
       </c>
@@ -6273,7 +6272,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>188</v>
       </c>
@@ -6332,7 +6331,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>188</v>
       </c>
@@ -6391,7 +6390,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>188</v>
       </c>
@@ -6450,7 +6449,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>188</v>
       </c>
@@ -6509,7 +6508,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>188</v>
       </c>
@@ -6568,7 +6567,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>200</v>
       </c>
@@ -6627,7 +6626,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>200</v>
       </c>
@@ -6686,7 +6685,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>200</v>
       </c>
@@ -6745,7 +6744,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>200</v>
       </c>
@@ -6804,7 +6803,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>217</v>
       </c>
@@ -6863,7 +6862,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>217</v>
       </c>
@@ -6922,7 +6921,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>217</v>
       </c>
@@ -6981,7 +6980,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>217</v>
       </c>
@@ -7040,7 +7039,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>217</v>
       </c>
@@ -7099,7 +7098,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>217</v>
       </c>
@@ -7158,7 +7157,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>217</v>
       </c>
@@ -7217,7 +7216,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>217</v>
       </c>
@@ -7276,7 +7275,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>229</v>
       </c>
@@ -7335,7 +7334,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>229</v>
       </c>
@@ -7394,7 +7393,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>229</v>
       </c>
@@ -7453,7 +7452,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>229</v>
       </c>
@@ -7512,7 +7511,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>249</v>
       </c>
@@ -7571,7 +7570,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>249</v>
       </c>
@@ -7630,7 +7629,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>249</v>
       </c>
@@ -7689,7 +7688,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>249</v>
       </c>
@@ -7748,7 +7747,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>249</v>
       </c>
@@ -7807,7 +7806,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>249</v>
       </c>
@@ -7866,7 +7865,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>249</v>
       </c>
@@ -7925,7 +7924,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>249</v>
       </c>
@@ -7984,7 +7983,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>249</v>
       </c>
@@ -8043,7 +8042,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>277</v>
       </c>
@@ -8102,7 +8101,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>277</v>
       </c>
@@ -8161,7 +8160,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>277</v>
       </c>
@@ -8220,7 +8219,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>277</v>
       </c>
@@ -8279,7 +8278,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>277</v>
       </c>
@@ -8338,7 +8337,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>277</v>
       </c>
@@ -8397,7 +8396,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>277</v>
       </c>
@@ -8456,7 +8455,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>277</v>
       </c>
@@ -8515,7 +8514,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>277</v>
       </c>
@@ -8574,7 +8573,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>277</v>
       </c>
@@ -8633,7 +8632,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>277</v>
       </c>
@@ -8692,7 +8691,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>300</v>
       </c>
@@ -8751,7 +8750,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>300</v>
       </c>
@@ -8810,7 +8809,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>300</v>
       </c>
@@ -8869,7 +8868,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>300</v>
       </c>
@@ -8928,7 +8927,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>300</v>
       </c>
@@ -8987,7 +8986,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>302</v>
       </c>
@@ -9046,7 +9045,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>302</v>
       </c>
@@ -9105,7 +9104,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>305</v>
       </c>
@@ -9164,7 +9163,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>305</v>
       </c>
@@ -9223,7 +9222,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>305</v>
       </c>
@@ -9282,7 +9281,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>305</v>
       </c>
@@ -9341,7 +9340,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>313</v>
       </c>
@@ -9400,7 +9399,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>313</v>
       </c>
@@ -9459,7 +9458,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>313</v>
       </c>
@@ -9518,7 +9517,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>313</v>
       </c>
@@ -9577,7 +9576,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>313</v>
       </c>
@@ -9636,7 +9635,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>328</v>
       </c>
@@ -9695,7 +9694,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>328</v>
       </c>
@@ -9754,7 +9753,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>328</v>
       </c>
@@ -9813,7 +9812,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>328</v>
       </c>
@@ -9872,7 +9871,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>328</v>
       </c>
@@ -9931,7 +9930,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>328</v>
       </c>
@@ -9990,7 +9989,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>334</v>
       </c>
@@ -10049,7 +10048,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>334</v>
       </c>
@@ -10108,7 +10107,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>334</v>
       </c>
@@ -10167,7 +10166,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>334</v>
       </c>
@@ -10226,7 +10225,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>334</v>
       </c>
@@ -10285,7 +10284,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>334</v>
       </c>
@@ -10344,7 +10343,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>347</v>
       </c>
@@ -10403,7 +10402,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>347</v>
       </c>
@@ -10462,7 +10461,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>347</v>
       </c>
@@ -10521,7 +10520,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>353</v>
       </c>
@@ -10580,7 +10579,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>353</v>
       </c>
@@ -10639,7 +10638,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>355</v>
       </c>
@@ -10698,7 +10697,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>355</v>
       </c>
@@ -10757,7 +10756,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>357</v>
       </c>
@@ -10816,7 +10815,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>357</v>
       </c>
@@ -10875,7 +10874,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>357</v>
       </c>
@@ -10934,7 +10933,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>357</v>
       </c>
@@ -10993,7 +10992,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>357</v>
       </c>
@@ -11052,7 +11051,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>359</v>
       </c>
@@ -11111,7 +11110,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>359</v>
       </c>
@@ -11170,7 +11169,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>361</v>
       </c>
@@ -11229,7 +11228,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>363</v>
       </c>
@@ -11288,7 +11287,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>363</v>
       </c>
@@ -11347,7 +11346,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>363</v>
       </c>
@@ -11406,7 +11405,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>363</v>
       </c>
@@ -11465,7 +11464,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>363</v>
       </c>
@@ -11524,7 +11523,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>369</v>
       </c>
@@ -11583,7 +11582,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>369</v>
       </c>
@@ -11642,7 +11641,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>369</v>
       </c>
@@ -11701,7 +11700,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>369</v>
       </c>
@@ -11760,7 +11759,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>369</v>
       </c>
@@ -11819,7 +11818,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>369</v>
       </c>
@@ -11878,7 +11877,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>369</v>
       </c>
@@ -11937,7 +11936,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>369</v>
       </c>
@@ -11996,7 +11995,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>369</v>
       </c>
@@ -12055,7 +12054,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>383</v>
       </c>
@@ -12114,7 +12113,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>383</v>
       </c>
@@ -12173,7 +12172,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>383</v>
       </c>
@@ -12232,7 +12231,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>383</v>
       </c>
@@ -12291,7 +12290,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>383</v>
       </c>
@@ -12350,7 +12349,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>383</v>
       </c>
@@ -12409,7 +12408,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>398</v>
       </c>
@@ -12468,7 +12467,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>398</v>
       </c>
@@ -12527,7 +12526,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>398</v>
       </c>
@@ -12586,7 +12585,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>398</v>
       </c>
@@ -12645,7 +12644,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>409</v>
       </c>
@@ -12704,7 +12703,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>409</v>
       </c>
@@ -12763,7 +12762,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>409</v>
       </c>
@@ -12822,7 +12821,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>409</v>
       </c>
@@ -12881,7 +12880,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>409</v>
       </c>
@@ -12940,7 +12939,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>409</v>
       </c>
@@ -12999,7 +12998,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>409</v>
       </c>
@@ -13058,7 +13057,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>409</v>
       </c>
@@ -13117,7 +13116,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>409</v>
       </c>
@@ -13176,7 +13175,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>423</v>
       </c>
@@ -13235,7 +13234,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>423</v>
       </c>
@@ -13294,7 +13293,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>423</v>
       </c>
@@ -13353,7 +13352,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>423</v>
       </c>
@@ -13412,7 +13411,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>423</v>
       </c>
@@ -13471,7 +13470,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>423</v>
       </c>
@@ -13530,7 +13529,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>433</v>
       </c>
@@ -13589,7 +13588,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>433</v>
       </c>
@@ -13648,7 +13647,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>433</v>
       </c>
@@ -13707,7 +13706,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>443</v>
       </c>
@@ -13766,7 +13765,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>443</v>
       </c>
@@ -13825,7 +13824,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>443</v>
       </c>
@@ -13884,7 +13883,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>446</v>
       </c>
@@ -13943,7 +13942,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>446</v>
       </c>
@@ -14002,7 +14001,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>446</v>
       </c>
@@ -14061,7 +14060,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>452</v>
       </c>
@@ -14120,7 +14119,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>455</v>
       </c>
@@ -14179,7 +14178,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>457</v>
       </c>
@@ -14238,7 +14237,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>457</v>
       </c>
@@ -14297,7 +14296,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>457</v>
       </c>
@@ -14356,7 +14355,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>459</v>
       </c>
@@ -14415,7 +14414,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>459</v>
       </c>
@@ -14474,7 +14473,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>469</v>
       </c>
@@ -14533,7 +14532,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>471</v>
       </c>
@@ -14592,7 +14591,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>471</v>
       </c>
@@ -14651,7 +14650,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>473</v>
       </c>
@@ -14710,7 +14709,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>473</v>
       </c>
@@ -14769,7 +14768,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>475</v>
       </c>
@@ -14828,7 +14827,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>477</v>
       </c>
@@ -14887,7 +14886,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>477</v>
       </c>
@@ -14946,7 +14945,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>479</v>
       </c>
@@ -15005,7 +15004,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>479</v>
       </c>
@@ -15064,7 +15063,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>479</v>
       </c>
@@ -15123,7 +15122,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>479</v>
       </c>
@@ -15182,7 +15181,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>485</v>
       </c>
@@ -15241,7 +15240,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>485</v>
       </c>
@@ -15300,7 +15299,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>485</v>
       </c>
@@ -15359,7 +15358,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>485</v>
       </c>
@@ -15418,7 +15417,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>485</v>
       </c>
@@ -15477,7 +15476,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>487</v>
       </c>
@@ -15536,7 +15535,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>487</v>
       </c>
@@ -15595,7 +15594,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>487</v>
       </c>
@@ -15654,7 +15653,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>487</v>
       </c>
@@ -15713,7 +15712,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>492</v>
       </c>
@@ -15772,7 +15771,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>492</v>
       </c>
@@ -15831,7 +15830,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>492</v>
       </c>
@@ -15890,7 +15889,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>492</v>
       </c>
@@ -15949,7 +15948,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>494</v>
       </c>
@@ -16008,7 +16007,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>494</v>
       </c>
@@ -16067,7 +16066,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>494</v>
       </c>
@@ -16126,7 +16125,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>496</v>
       </c>
@@ -16185,7 +16184,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>498</v>
       </c>
@@ -16244,7 +16243,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>498</v>
       </c>
@@ -16303,7 +16302,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>498</v>
       </c>
@@ -16362,7 +16361,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>498</v>
       </c>
@@ -16421,7 +16420,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>498</v>
       </c>
@@ -16480,7 +16479,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>498</v>
       </c>
@@ -16539,7 +16538,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>498</v>
       </c>
@@ -16598,7 +16597,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>498</v>
       </c>
@@ -16657,7 +16656,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>503</v>
       </c>
@@ -16716,7 +16715,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>503</v>
       </c>
@@ -16775,7 +16774,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>503</v>
       </c>
@@ -16834,7 +16833,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>503</v>
       </c>
@@ -16893,7 +16892,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>503</v>
       </c>
@@ -16952,7 +16951,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>503</v>
       </c>
@@ -17011,7 +17010,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>503</v>
       </c>
@@ -17070,7 +17069,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>503</v>
       </c>
@@ -17129,7 +17128,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>503</v>
       </c>
@@ -17188,7 +17187,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>516</v>
       </c>
@@ -17247,7 +17246,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>516</v>
       </c>
@@ -17306,7 +17305,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>516</v>
       </c>
@@ -17365,7 +17364,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>516</v>
       </c>
@@ -17424,7 +17423,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>516</v>
       </c>
@@ -17483,7 +17482,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>516</v>
       </c>
@@ -17542,7 +17541,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>516</v>
       </c>
@@ -17601,7 +17600,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>516</v>
       </c>
@@ -17660,7 +17659,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>516</v>
       </c>
@@ -17719,7 +17718,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>530</v>
       </c>
@@ -17778,7 +17777,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>530</v>
       </c>
@@ -17837,7 +17836,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>530</v>
       </c>
@@ -17896,7 +17895,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>530</v>
       </c>
@@ -17955,7 +17954,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>530</v>
       </c>
@@ -18014,7 +18013,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>530</v>
       </c>
@@ -18073,7 +18072,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>530</v>
       </c>
@@ -18132,7 +18131,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>530</v>
       </c>
@@ -18191,7 +18190,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>530</v>
       </c>
@@ -18250,7 +18249,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>536</v>
       </c>
@@ -18309,7 +18308,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>536</v>
       </c>
@@ -18368,7 +18367,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>536</v>
       </c>
@@ -18427,7 +18426,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>536</v>
       </c>
@@ -18486,7 +18485,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>536</v>
       </c>
@@ -18545,7 +18544,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>536</v>
       </c>
@@ -18604,7 +18603,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>536</v>
       </c>
@@ -18663,7 +18662,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>547</v>
       </c>
@@ -18722,7 +18721,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>547</v>
       </c>
@@ -18781,7 +18780,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>547</v>
       </c>
@@ -18840,7 +18839,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>549</v>
       </c>
@@ -18899,7 +18898,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>549</v>
       </c>
@@ -18958,7 +18957,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>549</v>
       </c>
@@ -19017,7 +19016,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>549</v>
       </c>
@@ -19076,7 +19075,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>549</v>
       </c>
@@ -19135,7 +19134,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>555</v>
       </c>
@@ -19194,7 +19193,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>555</v>
       </c>
@@ -19253,7 +19252,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>555</v>
       </c>
@@ -19312,7 +19311,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>555</v>
       </c>
@@ -19371,7 +19370,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>555</v>
       </c>
@@ -19430,7 +19429,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>555</v>
       </c>
@@ -19489,7 +19488,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>564</v>
       </c>
@@ -19548,7 +19547,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>564</v>
       </c>
@@ -19607,7 +19606,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>575</v>
       </c>
@@ -19666,7 +19665,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>575</v>
       </c>
@@ -19725,7 +19724,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>575</v>
       </c>
@@ -19784,7 +19783,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>575</v>
       </c>
@@ -19843,7 +19842,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>575</v>
       </c>
@@ -19902,7 +19901,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>575</v>
       </c>
@@ -19961,7 +19960,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>575</v>
       </c>
@@ -20020,7 +20019,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>575</v>
       </c>
@@ -20079,7 +20078,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>575</v>
       </c>
@@ -20138,7 +20137,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>577</v>
       </c>
@@ -20197,7 +20196,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>577</v>
       </c>
@@ -20256,7 +20255,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>577</v>
       </c>
@@ -20315,7 +20314,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>586</v>
       </c>
@@ -20374,7 +20373,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>586</v>
       </c>
@@ -20433,7 +20432,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>586</v>
       </c>
@@ -20492,7 +20491,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>586</v>
       </c>
@@ -20551,7 +20550,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>586</v>
       </c>
@@ -20610,7 +20609,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>586</v>
       </c>
@@ -20669,7 +20668,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>586</v>
       </c>
@@ -20728,7 +20727,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>586</v>
       </c>
@@ -20787,7 +20786,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>593</v>
       </c>
@@ -20846,7 +20845,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>593</v>
       </c>
@@ -20905,7 +20904,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>593</v>
       </c>
@@ -20964,7 +20963,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>593</v>
       </c>
@@ -21023,7 +21022,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>593</v>
       </c>
@@ -21082,7 +21081,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>593</v>
       </c>
@@ -21141,7 +21140,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="304" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>593</v>
       </c>
@@ -21200,7 +21199,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>593</v>
       </c>
@@ -21259,7 +21258,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>593</v>
       </c>
@@ -21318,7 +21317,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>593</v>
       </c>
@@ -21377,7 +21376,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>593</v>
       </c>
@@ -21436,7 +21435,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>593</v>
       </c>
@@ -21495,7 +21494,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>626</v>
       </c>
@@ -21554,7 +21553,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>626</v>
       </c>
@@ -21613,7 +21612,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>626</v>
       </c>
@@ -21672,7 +21671,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>626</v>
       </c>
@@ -21731,7 +21730,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>626</v>
       </c>
@@ -21790,7 +21789,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>626</v>
       </c>
@@ -21849,7 +21848,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>626</v>
       </c>
@@ -21908,7 +21907,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>641</v>
       </c>
@@ -21967,7 +21966,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>641</v>
       </c>
@@ -22026,7 +22025,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>641</v>
       </c>
@@ -22085,7 +22084,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>641</v>
       </c>
@@ -22144,7 +22143,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>641</v>
       </c>
@@ -22203,7 +22202,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>641</v>
       </c>
@@ -22262,7 +22261,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>641</v>
       </c>
@@ -22321,7 +22320,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>641</v>
       </c>
@@ -22380,7 +22379,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>641</v>
       </c>
@@ -22439,7 +22438,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>641</v>
       </c>
@@ -22498,7 +22497,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>654</v>
       </c>
@@ -22557,7 +22556,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>654</v>
       </c>
@@ -22616,7 +22615,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>654</v>
       </c>
@@ -22675,7 +22674,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>654</v>
       </c>
@@ -22734,7 +22733,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>654</v>
       </c>
@@ -22793,7 +22792,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>654</v>
       </c>
@@ -22852,7 +22851,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>654</v>
       </c>
@@ -22911,7 +22910,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>654</v>
       </c>
@@ -22970,7 +22969,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>665</v>
       </c>
@@ -23029,7 +23028,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>665</v>
       </c>
@@ -23088,7 +23087,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>665</v>
       </c>
@@ -23147,7 +23146,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>665</v>
       </c>
@@ -23206,7 +23205,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>665</v>
       </c>
@@ -23265,7 +23264,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>671</v>
       </c>
@@ -23324,7 +23323,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>677</v>
       </c>
@@ -23383,7 +23382,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>677</v>
       </c>
@@ -23442,7 +23441,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>677</v>
       </c>
@@ -23501,7 +23500,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>677</v>
       </c>
@@ -23560,7 +23559,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>677</v>
       </c>
@@ -23619,7 +23618,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>677</v>
       </c>
@@ -23675,7 +23674,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>677</v>
       </c>
@@ -23734,7 +23733,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>677</v>
       </c>
@@ -23793,7 +23792,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>677</v>
       </c>
@@ -23852,7 +23851,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>677</v>
       </c>
@@ -23911,7 +23910,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>677</v>
       </c>
@@ -23970,7 +23969,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>677</v>
       </c>
@@ -24029,7 +24028,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>693</v>
       </c>
@@ -24088,7 +24087,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>693</v>
       </c>
@@ -24147,7 +24146,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>693</v>
       </c>
@@ -24206,7 +24205,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>693</v>
       </c>
@@ -24265,7 +24264,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>693</v>
       </c>
@@ -24324,7 +24323,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>693</v>
       </c>
@@ -24383,7 +24382,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>693</v>
       </c>
@@ -24442,7 +24441,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>693</v>
       </c>
@@ -24501,7 +24500,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>693</v>
       </c>
@@ -24560,7 +24559,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>695</v>
       </c>
@@ -24619,7 +24618,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>695</v>
       </c>
@@ -24678,7 +24677,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>695</v>
       </c>
@@ -24737,7 +24736,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>695</v>
       </c>
@@ -24796,7 +24795,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>695</v>
       </c>
@@ -24855,7 +24854,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>695</v>
       </c>
@@ -24914,7 +24913,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>695</v>
       </c>
@@ -24973,7 +24972,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>695</v>
       </c>
@@ -25032,7 +25031,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>695</v>
       </c>
@@ -25091,7 +25090,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>705</v>
       </c>
@@ -25150,7 +25149,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>705</v>
       </c>
@@ -25209,7 +25208,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>705</v>
       </c>
@@ -25268,7 +25267,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>705</v>
       </c>
@@ -25327,7 +25326,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>705</v>
       </c>
@@ -25386,7 +25385,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>705</v>
       </c>
@@ -25445,7 +25444,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>705</v>
       </c>
@@ -25504,7 +25503,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>705</v>
       </c>
@@ -25563,7 +25562,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>705</v>
       </c>
@@ -25622,7 +25621,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>705</v>
       </c>
@@ -25681,7 +25680,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>705</v>
       </c>
@@ -25740,7 +25739,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>705</v>
       </c>
@@ -25799,7 +25798,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>705</v>
       </c>
@@ -25858,7 +25857,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>705</v>
       </c>
@@ -25917,7 +25916,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>705</v>
       </c>
@@ -25976,7 +25975,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>705</v>
       </c>
@@ -26035,7 +26034,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>705</v>
       </c>
@@ -26094,7 +26093,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>716</v>
       </c>
@@ -26153,7 +26152,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>716</v>
       </c>
@@ -26212,7 +26211,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>716</v>
       </c>
@@ -26271,7 +26270,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>716</v>
       </c>
@@ -26330,7 +26329,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>716</v>
       </c>
@@ -26389,7 +26388,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>716</v>
       </c>
@@ -26448,7 +26447,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>716</v>
       </c>
@@ -26507,7 +26506,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>716</v>
       </c>
@@ -26566,7 +26565,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>716</v>
       </c>
@@ -26625,7 +26624,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>716</v>
       </c>
@@ -26684,7 +26683,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>716</v>
       </c>
@@ -26743,7 +26742,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>716</v>
       </c>
@@ -26802,7 +26801,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>737</v>
       </c>
@@ -26861,7 +26860,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>737</v>
       </c>
@@ -26920,7 +26919,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>737</v>
       </c>
@@ -26979,7 +26978,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>737</v>
       </c>
@@ -27038,7 +27037,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>737</v>
       </c>
@@ -27097,7 +27096,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>737</v>
       </c>
@@ -27156,7 +27155,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>737</v>
       </c>
@@ -27215,7 +27214,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>737</v>
       </c>
@@ -27274,7 +27273,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>737</v>
       </c>
@@ -27333,7 +27332,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>746</v>
       </c>
@@ -27392,7 +27391,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>746</v>
       </c>
@@ -27451,7 +27450,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>746</v>
       </c>
@@ -27510,7 +27509,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>746</v>
       </c>
@@ -27569,7 +27568,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>746</v>
       </c>
@@ -27628,7 +27627,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>746</v>
       </c>
@@ -27687,7 +27686,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>746</v>
       </c>
@@ -27746,7 +27745,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>746</v>
       </c>
@@ -27805,7 +27804,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>746</v>
       </c>
@@ -27864,7 +27863,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>752</v>
       </c>
@@ -27923,7 +27922,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>752</v>
       </c>
@@ -27982,7 +27981,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>752</v>
       </c>
@@ -28041,7 +28040,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>752</v>
       </c>
@@ -28100,7 +28099,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>752</v>
       </c>
@@ -28159,7 +28158,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>752</v>
       </c>
@@ -28218,7 +28217,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>752</v>
       </c>
@@ -28277,7 +28276,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>752</v>
       </c>
@@ -28336,7 +28335,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>752</v>
       </c>
@@ -28395,7 +28394,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>752</v>
       </c>
@@ -28454,7 +28453,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>758</v>
       </c>
@@ -28513,7 +28512,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>758</v>
       </c>
@@ -28572,7 +28571,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>758</v>
       </c>
@@ -28631,7 +28630,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>758</v>
       </c>
@@ -28690,7 +28689,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>758</v>
       </c>
@@ -28749,7 +28748,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>758</v>
       </c>
@@ -28808,7 +28807,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>758</v>
       </c>
@@ -28867,7 +28866,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>758</v>
       </c>
@@ -28926,7 +28925,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="436" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>758</v>
       </c>
@@ -28985,7 +28984,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>758</v>
       </c>
@@ -29044,7 +29043,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>758</v>
       </c>
@@ -29103,7 +29102,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>773</v>
       </c>
@@ -29162,7 +29161,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>773</v>
       </c>
@@ -29221,7 +29220,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>773</v>
       </c>
@@ -29280,7 +29279,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>773</v>
       </c>
@@ -29339,7 +29338,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>773</v>
       </c>
@@ -29398,7 +29397,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="444" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>773</v>
       </c>
@@ -29457,7 +29456,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>773</v>
       </c>
@@ -29516,7 +29515,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>773</v>
       </c>
@@ -29575,7 +29574,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>773</v>
       </c>
@@ -29634,7 +29633,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>773</v>
       </c>
@@ -29693,7 +29692,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="449" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>773</v>
       </c>
@@ -29752,7 +29751,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="450" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>783</v>
       </c>
@@ -29814,7 +29813,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="451" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>783</v>
       </c>
@@ -29873,7 +29872,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="452" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>783</v>
       </c>
@@ -29932,7 +29931,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="453" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>783</v>
       </c>
@@ -29991,7 +29990,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="454" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>783</v>
       </c>
@@ -30050,7 +30049,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="455" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>783</v>
       </c>
@@ -30109,7 +30108,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="456" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>783</v>
       </c>
@@ -30168,7 +30167,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="457" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>783</v>
       </c>
@@ -30230,7 +30229,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="458" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>783</v>
       </c>
@@ -30289,7 +30288,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="459" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>783</v>
       </c>
@@ -30348,7 +30347,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="460" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>783</v>
       </c>
@@ -30407,7 +30406,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="461" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>783</v>
       </c>
@@ -30466,7 +30465,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="462" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>783</v>
       </c>
@@ -30525,7 +30524,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="463" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>794</v>
       </c>
@@ -30584,7 +30583,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="464" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>794</v>
       </c>
@@ -30643,7 +30642,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>794</v>
       </c>
@@ -30702,7 +30701,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>794</v>
       </c>
@@ -30761,7 +30760,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>794</v>
       </c>
@@ -30820,7 +30819,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>794</v>
       </c>
@@ -30879,7 +30878,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>794</v>
       </c>
@@ -30938,7 +30937,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>794</v>
       </c>
@@ -30997,7 +30996,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>794</v>
       </c>
@@ -31056,7 +31055,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>794</v>
       </c>
@@ -31115,7 +31114,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>794</v>
       </c>
@@ -31174,7 +31173,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>794</v>
       </c>
@@ -31233,7 +31232,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>794</v>
       </c>
@@ -31292,7 +31291,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>794</v>
       </c>
@@ -31351,7 +31350,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>794</v>
       </c>
@@ -31410,7 +31409,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>794</v>
       </c>
@@ -31469,7 +31468,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>794</v>
       </c>
@@ -31528,7 +31527,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>794</v>
       </c>
@@ -31587,7 +31586,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>813</v>
       </c>
@@ -31646,7 +31645,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>813</v>
       </c>
@@ -31705,7 +31704,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>813</v>
       </c>
@@ -31764,7 +31763,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>813</v>
       </c>
@@ -31823,7 +31822,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>813</v>
       </c>
@@ -31882,7 +31881,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>813</v>
       </c>
@@ -31941,7 +31940,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>813</v>
       </c>
@@ -32000,7 +31999,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>813</v>
       </c>
@@ -32059,7 +32058,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>823</v>
       </c>
@@ -32118,7 +32117,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>823</v>
       </c>
@@ -32177,7 +32176,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>823</v>
       </c>
@@ -32236,7 +32235,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>823</v>
       </c>
@@ -32295,7 +32294,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>823</v>
       </c>
@@ -32354,7 +32353,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>823</v>
       </c>
@@ -32413,7 +32412,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>823</v>
       </c>
@@ -32472,7 +32471,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>823</v>
       </c>
@@ -32531,7 +32530,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="497" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>823</v>
       </c>
@@ -32590,7 +32589,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="498" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>823</v>
       </c>
@@ -32649,7 +32648,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="499" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>823</v>
       </c>
@@ -32708,7 +32707,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="500" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>823</v>
       </c>
@@ -32767,7 +32766,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="501" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>823</v>
       </c>
@@ -32826,7 +32825,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="502" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>823</v>
       </c>
@@ -32885,7 +32884,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="503" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>841</v>
       </c>
@@ -32944,7 +32943,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="504" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>841</v>
       </c>
@@ -33003,7 +33002,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="505" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>841</v>
       </c>
@@ -33065,7 +33064,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="506" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>841</v>
       </c>
@@ -33124,7 +33123,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="507" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>841</v>
       </c>
@@ -33183,7 +33182,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="508" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>841</v>
       </c>
@@ -33242,7 +33241,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="509" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>841</v>
       </c>
@@ -33301,7 +33300,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="510" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>841</v>
       </c>
@@ -33360,7 +33359,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="511" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>841</v>
       </c>
@@ -33419,7 +33418,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="512" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>841</v>
       </c>
@@ -33478,7 +33477,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="513" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>841</v>
       </c>
@@ -33537,7 +33536,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>841</v>
       </c>
@@ -33596,7 +33595,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>841</v>
       </c>
@@ -33655,7 +33654,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>841</v>
       </c>
@@ -33714,7 +33713,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>853</v>
       </c>
@@ -33773,7 +33772,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>853</v>
       </c>
@@ -33832,7 +33831,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>853</v>
       </c>
@@ -33891,7 +33890,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>853</v>
       </c>
@@ -33950,7 +33949,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>853</v>
       </c>
@@ -34009,7 +34008,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>853</v>
       </c>
@@ -34068,7 +34067,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>853</v>
       </c>
@@ -34127,7 +34126,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>853</v>
       </c>
@@ -34186,7 +34185,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>853</v>
       </c>
@@ -34245,7 +34244,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>853</v>
       </c>
@@ -34304,7 +34303,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>853</v>
       </c>
@@ -34363,7 +34362,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>853</v>
       </c>
@@ -34422,7 +34421,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>853</v>
       </c>
@@ -34481,7 +34480,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>873</v>
       </c>
@@ -34540,7 +34539,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>873</v>
       </c>
@@ -34599,7 +34598,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>873</v>
       </c>
@@ -34658,7 +34657,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>873</v>
       </c>
@@ -34717,7 +34716,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>873</v>
       </c>
@@ -34776,7 +34775,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>873</v>
       </c>
@@ -34835,7 +34834,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>873</v>
       </c>
@@ -34894,7 +34893,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>873</v>
       </c>
@@ -34953,7 +34952,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>873</v>
       </c>
@@ -35012,7 +35011,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>873</v>
       </c>
@@ -35071,7 +35070,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>873</v>
       </c>
@@ -35130,7 +35129,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>873</v>
       </c>
@@ -35189,7 +35188,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>873</v>
       </c>
@@ -35248,7 +35247,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>873</v>
       </c>
@@ -35307,7 +35306,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>873</v>
       </c>
@@ -35366,7 +35365,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>873</v>
       </c>
@@ -35425,7 +35424,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>882</v>
       </c>
@@ -35484,7 +35483,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>882</v>
       </c>
@@ -35543,7 +35542,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>882</v>
       </c>
@@ -35602,7 +35601,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>882</v>
       </c>
@@ -35661,7 +35660,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>882</v>
       </c>
@@ -35720,7 +35719,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>882</v>
       </c>
@@ -35779,7 +35778,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>882</v>
       </c>
@@ -35838,7 +35837,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>882</v>
       </c>
@@ -35897,7 +35896,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>882</v>
       </c>
@@ -35956,7 +35955,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>882</v>
       </c>
@@ -36015,7 +36014,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>882</v>
       </c>
@@ -36074,7 +36073,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>882</v>
       </c>
@@ -36133,7 +36132,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>882</v>
       </c>
@@ -36192,7 +36191,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>882</v>
       </c>
@@ -36251,7 +36250,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>882</v>
       </c>
@@ -36310,7 +36309,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>882</v>
       </c>
@@ -36369,7 +36368,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="562" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>882</v>
       </c>
@@ -36428,7 +36427,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>888</v>
       </c>
@@ -36487,7 +36486,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>888</v>
       </c>
@@ -36546,7 +36545,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>888</v>
       </c>
@@ -36605,7 +36604,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>888</v>
       </c>
@@ -36664,7 +36663,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>888</v>
       </c>
@@ -36723,7 +36722,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>888</v>
       </c>
@@ -36782,7 +36781,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>888</v>
       </c>
@@ -36841,7 +36840,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="570" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>888</v>
       </c>
@@ -36900,7 +36899,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>893</v>
       </c>
@@ -36959,7 +36958,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>893</v>
       </c>
@@ -37018,7 +37017,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>893</v>
       </c>
@@ -37077,7 +37076,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="574" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>893</v>
       </c>
@@ -37136,7 +37135,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>893</v>
       </c>
@@ -37195,7 +37194,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>893</v>
       </c>
@@ -37254,7 +37253,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>893</v>
       </c>
@@ -37313,7 +37312,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>893</v>
       </c>
@@ -37372,7 +37371,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>893</v>
       </c>
@@ -37431,7 +37430,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="580" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>893</v>
       </c>
@@ -37490,7 +37489,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>893</v>
       </c>
@@ -37549,7 +37548,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>893</v>
       </c>
@@ -37608,7 +37607,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="583" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>893</v>
       </c>
@@ -37667,7 +37666,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>893</v>
       </c>
@@ -37726,7 +37725,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>893</v>
       </c>
@@ -37785,7 +37784,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>893</v>
       </c>
@@ -37844,7 +37843,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>893</v>
       </c>
@@ -37903,7 +37902,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="588" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>893</v>
       </c>
@@ -37962,7 +37961,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>903</v>
       </c>
@@ -38021,7 +38020,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>903</v>
       </c>
@@ -38080,7 +38079,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>903</v>
       </c>
@@ -38139,7 +38138,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>903</v>
       </c>
@@ -38198,7 +38197,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>903</v>
       </c>
@@ -38257,7 +38256,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>903</v>
       </c>
@@ -38316,7 +38315,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>903</v>
       </c>
@@ -38375,7 +38374,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="596" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>903</v>
       </c>
@@ -38434,7 +38433,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>903</v>
       </c>
@@ -38493,7 +38492,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>903</v>
       </c>
@@ -38552,7 +38551,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>903</v>
       </c>
@@ -38611,7 +38610,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>903</v>
       </c>
@@ -38670,7 +38669,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="601" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>903</v>
       </c>
@@ -38729,7 +38728,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>903</v>
       </c>
@@ -38788,7 +38787,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>903</v>
       </c>
@@ -38847,7 +38846,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="604" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>903</v>
       </c>
@@ -38906,7 +38905,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>903</v>
       </c>
@@ -38965,7 +38964,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>903</v>
       </c>
@@ -39024,7 +39023,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>903</v>
       </c>
@@ -39083,7 +39082,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="608" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>915</v>
       </c>
@@ -39142,7 +39141,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>915</v>
       </c>
@@ -39201,7 +39200,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>915</v>
       </c>
@@ -39260,7 +39259,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>915</v>
       </c>
@@ -39319,7 +39318,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>915</v>
       </c>
@@ -39378,7 +39377,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="613" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>915</v>
       </c>
@@ -39437,7 +39436,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>915</v>
       </c>
@@ -39496,7 +39495,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>915</v>
       </c>
@@ -39555,7 +39554,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>915</v>
       </c>
@@ -39614,7 +39613,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="617" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>915</v>
       </c>
@@ -39673,7 +39672,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>915</v>
       </c>
@@ -39732,7 +39731,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>915</v>
       </c>
@@ -39791,7 +39790,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>920</v>
       </c>
@@ -39850,7 +39849,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>920</v>
       </c>
@@ -39909,7 +39908,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="622" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>920</v>
       </c>
@@ -39968,7 +39967,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>920</v>
       </c>
@@ -40027,7 +40026,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>920</v>
       </c>
@@ -40086,7 +40085,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>920</v>
       </c>
@@ -40145,7 +40144,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>922</v>
       </c>
@@ -40204,7 +40203,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>922</v>
       </c>
@@ -40263,7 +40262,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>922</v>
       </c>
@@ -40322,7 +40321,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>922</v>
       </c>
@@ -40381,7 +40380,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>922</v>
       </c>
@@ -40440,7 +40439,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>922</v>
       </c>
@@ -40499,7 +40498,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>922</v>
       </c>
@@ -40558,7 +40557,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="633" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>922</v>
       </c>
@@ -40617,7 +40616,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>922</v>
       </c>
@@ -40676,7 +40675,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>922</v>
       </c>
@@ -40735,7 +40734,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>922</v>
       </c>
@@ -40794,7 +40793,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>922</v>
       </c>
@@ -40853,7 +40852,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>922</v>
       </c>
@@ -40912,7 +40911,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>922</v>
       </c>
@@ -40971,7 +40970,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>922</v>
       </c>
@@ -41562,13 +41561,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T649" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Q100"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T649" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
